--- a/artfynd/A 2021-2022 artfynd.xlsx
+++ b/artfynd/A 2021-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 2021-2022 artfynd.xlsx
+++ b/artfynd/A 2021-2022 artfynd.xlsx
@@ -1839,10 +1839,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118237569</v>
+        <v>118237484</v>
       </c>
       <c r="B12" t="n">
-        <v>57306</v>
+        <v>90524</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1855,46 +1855,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Funbo Åkerby, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>656120</v>
+        <v>656154</v>
       </c>
       <c r="R12" t="n">
-        <v>6639931</v>
+        <v>6639881</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1950,10 +1941,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118237570</v>
+        <v>118237468</v>
       </c>
       <c r="B13" t="n">
-        <v>57694</v>
+        <v>104853</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1962,50 +1953,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103037</v>
+        <v>221141</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Funbo Åkerby, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>656175</v>
+        <v>656182</v>
       </c>
       <c r="R13" t="n">
-        <v>6639828</v>
+        <v>6639863</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2061,10 +2043,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118237484</v>
+        <v>118237483</v>
       </c>
       <c r="B14" t="n">
-        <v>90524</v>
+        <v>100107</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2073,25 +2055,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2101,13 +2083,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>656154</v>
+        <v>656097</v>
       </c>
       <c r="R14" t="n">
-        <v>6639881</v>
+        <v>6639678</v>
       </c>
       <c r="S14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2163,10 +2145,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118237568</v>
+        <v>118237470</v>
       </c>
       <c r="B15" t="n">
-        <v>57623</v>
+        <v>104853</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2175,50 +2157,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103008</v>
+        <v>221141</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Funbo Åkerby, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>656124</v>
+        <v>656171</v>
       </c>
       <c r="R15" t="n">
-        <v>6639712</v>
+        <v>6639830</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2274,10 +2247,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118237483</v>
+        <v>118237569</v>
       </c>
       <c r="B16" t="n">
-        <v>100107</v>
+        <v>57306</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2286,41 +2259,50 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Funbo Åkerby, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>656097</v>
+        <v>656120</v>
       </c>
       <c r="R16" t="n">
-        <v>6639678</v>
+        <v>6639931</v>
       </c>
       <c r="S16" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2376,10 +2358,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118237468</v>
+        <v>118237570</v>
       </c>
       <c r="B17" t="n">
-        <v>104853</v>
+        <v>57694</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2388,41 +2370,50 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221141</v>
+        <v>103037</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Funbo Åkerby, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>656182</v>
+        <v>656175</v>
       </c>
       <c r="R17" t="n">
-        <v>6639863</v>
+        <v>6639828</v>
       </c>
       <c r="S17" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2478,10 +2469,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118237470</v>
+        <v>118237568</v>
       </c>
       <c r="B18" t="n">
-        <v>104853</v>
+        <v>57623</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2490,41 +2481,50 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221141</v>
+        <v>103008</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Funbo Åkerby, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>656171</v>
+        <v>656124</v>
       </c>
       <c r="R18" t="n">
-        <v>6639830</v>
+        <v>6639712</v>
       </c>
       <c r="S18" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>

--- a/artfynd/A 2021-2022 artfynd.xlsx
+++ b/artfynd/A 2021-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>109852562</v>
+        <v>109852553</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>655807.5344669642</v>
+        <v>656032</v>
       </c>
       <c r="R2" t="n">
-        <v>6639709.195110943</v>
+        <v>6639903</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,21 +743,11 @@
           <t>2023-05-05</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-05-05</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -771,6 +756,11 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -787,54 +777,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>109852563</v>
+        <v>109852555</v>
       </c>
       <c r="B3" t="n">
-        <v>103178</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221141</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Funbo-Åkerby, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>655812.1862411026</v>
+        <v>656030</v>
       </c>
       <c r="R3" t="n">
-        <v>6639706.373663004</v>
+        <v>6639851</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,26 +845,11 @@
           <t>2023-05-05</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-05-05</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Kluster med gullviva på gammal betesmark/backe med ask och blåsippa.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -892,6 +858,11 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -908,37 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>109852558</v>
+        <v>109852556</v>
       </c>
       <c r="B4" t="n">
-        <v>103178</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221141</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -948,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>655807.1932856076</v>
+        <v>656013</v>
       </c>
       <c r="R4" t="n">
-        <v>6639729.293972063</v>
+        <v>6639873</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,21 +947,11 @@
           <t>2023-05-05</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-05-05</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1004,6 +960,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1020,53 +981,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>109852560</v>
+        <v>118237484</v>
       </c>
       <c r="B5" t="n">
-        <v>73700</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6471</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulvit blekspik</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sclerophora pallida</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) Y.J.Jao &amp; Spooner</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Funbo-Åkerby, Upl</t>
+          <t>Funbo Åkerby, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>655803.5542878646</v>
+        <v>656154</v>
       </c>
       <c r="R5" t="n">
-        <v>6639708.022141793</v>
+        <v>6639881</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1090,22 +1046,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-05-05</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-05-05</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,11 +1062,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Ask</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1137,54 +1078,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>109852564</v>
+        <v>109852554</v>
       </c>
       <c r="B6" t="n">
-        <v>103178</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221141</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Funbo-Åkerby, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>655796.3252447881</v>
+        <v>656033</v>
       </c>
       <c r="R6" t="n">
-        <v>6639712.24376167</v>
+        <v>6639880</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1214,24 +1146,9 @@
           <t>2023-05-05</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-05-05</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Blommar på liten höjd som ser ut att vara tidigare betesmark. Står en grov ask bredvid</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,12 +1178,7 @@
         <v>109852559</v>
       </c>
       <c r="B7" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1298,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>655804.602080423</v>
+        <v>655804</v>
       </c>
       <c r="R7" t="n">
-        <v>6639707.06052195</v>
+        <v>6639707</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1331,19 +1243,9 @@
           <t>2023-05-05</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-05-05</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1375,37 +1277,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>109852554</v>
+        <v>109852560</v>
       </c>
       <c r="B8" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83314</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5966</v>
+        <v>6471</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Gulvit blekspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Sclerophora pallida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Pers.) Y.J.Jao &amp; Spooner</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1415,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>656033.0435991209</v>
+        <v>655803</v>
       </c>
       <c r="R8" t="n">
-        <v>6639880.087301379</v>
+        <v>6639708</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1448,21 +1345,11 @@
           <t>2023-05-05</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-05-05</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1471,6 +1358,11 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1487,37 +1379,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>109852561</v>
+        <v>116899798</v>
       </c>
       <c r="B9" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220785</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1525,19 +1412,27 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Funbo-Åkerby, Upl</t>
+          <t>Åkerby, Funbo, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>655803.6386834383</v>
+        <v>656099</v>
       </c>
       <c r="R9" t="n">
-        <v>6639706.014362636</v>
+        <v>6639901</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1561,27 +1456,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-05-05</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-05-05</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Grov ask på tidigare betesmark (sedan igenvuxen och nu del av slutavverkat område). Finns gullviva o blåsippa intill. Trädet hyser även gulvit blekspik som är hotad.</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1608,53 +1488,57 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>109852555</v>
+        <v>118237569</v>
       </c>
       <c r="B10" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Funbo-Åkerby, Upl</t>
+          <t>Funbo Åkerby, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>656030.7497119359</v>
+        <v>656120</v>
       </c>
       <c r="R10" t="n">
-        <v>6639850.827556828</v>
+        <v>6639931</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1678,22 +1562,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-05-05</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-05-05</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1704,11 +1578,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Tall</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1725,32 +1594,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>116899798</v>
+        <v>118237573</v>
       </c>
       <c r="B11" t="n">
-        <v>57294</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58463</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>102995</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1763,24 +1627,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Åkerby, Funbo, Upl</t>
+          <t>Funbo Åkerby, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>656099</v>
+        <v>656138</v>
       </c>
       <c r="R11" t="n">
-        <v>6639901</v>
+        <v>6639787</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1839,53 +1700,57 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118237484</v>
+        <v>118237568</v>
       </c>
       <c r="B12" t="n">
-        <v>90524</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58286</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>103008</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Funbo Åkerby, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>656154</v>
+        <v>656124</v>
       </c>
       <c r="R12" t="n">
-        <v>6639881</v>
+        <v>6639712</v>
       </c>
       <c r="S12" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1941,53 +1806,57 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118237468</v>
+        <v>118237570</v>
       </c>
       <c r="B13" t="n">
-        <v>104853</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58353</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221141</v>
+        <v>103037</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Funbo Åkerby, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>656182</v>
+        <v>656175</v>
       </c>
       <c r="R13" t="n">
-        <v>6639863</v>
+        <v>6639828</v>
       </c>
       <c r="S13" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2043,15 +1912,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118237483</v>
+        <v>118237572</v>
       </c>
       <c r="B14" t="n">
-        <v>100107</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58636</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2059,37 +1923,51 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>103044</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>föda åt ungar</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Funbo Åkerby, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>656097</v>
+        <v>656208</v>
       </c>
       <c r="R14" t="n">
-        <v>6639678</v>
+        <v>6639892</v>
       </c>
       <c r="S14" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2145,32 +2023,27 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118237470</v>
+        <v>109852561</v>
       </c>
       <c r="B15" t="n">
-        <v>104853</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221141</v>
+        <v>220785</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2178,20 +2051,24 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Funbo Åkerby, Upl</t>
+          <t>Funbo-Åkerby, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>656171</v>
+        <v>655803</v>
       </c>
       <c r="R15" t="n">
-        <v>6639830</v>
+        <v>6639706</v>
       </c>
       <c r="S15" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2215,12 +2092,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2023-05-05</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2023-05-05</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Grov ask på tidigare betesmark (sedan igenvuxen och nu del av slutavverkat område). Finns gullviva o blåsippa intill. Trädet hyser även gulvit blekspik som är hotad.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2247,62 +2129,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118237569</v>
+        <v>109852558</v>
       </c>
       <c r="B16" t="n">
-        <v>57306</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106156</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>221141</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Funbo Åkerby, Upl</t>
+          <t>Funbo-Åkerby, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>656120</v>
+        <v>655807</v>
       </c>
       <c r="R16" t="n">
-        <v>6639931</v>
+        <v>6639729</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2326,12 +2194,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2023-05-05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2023-05-05</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2358,62 +2226,52 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118237570</v>
+        <v>109852563</v>
       </c>
       <c r="B17" t="n">
-        <v>57694</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106156</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103037</v>
+        <v>221141</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Funbo Åkerby, Upl</t>
+          <t>Funbo-Åkerby, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>656175</v>
+        <v>655812</v>
       </c>
       <c r="R17" t="n">
-        <v>6639828</v>
+        <v>6639706</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2437,12 +2295,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2023-05-05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2023-05-05</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Kluster med gullviva på gammal betesmark/backe med ask och blåsippa.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2469,62 +2332,52 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118237568</v>
+        <v>109852564</v>
       </c>
       <c r="B18" t="n">
-        <v>57623</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106156</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103008</v>
+        <v>221141</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Funbo Åkerby, Upl</t>
+          <t>Funbo-Åkerby, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>656124</v>
+        <v>655797</v>
       </c>
       <c r="R18" t="n">
         <v>6639712</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2548,12 +2401,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2023-05-05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2023-05-05</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Blommar på liten höjd som ser ut att vara tidigare betesmark. Står en grov ask bredvid</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2577,6 +2435,976 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>118237468</v>
+      </c>
+      <c r="B19" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Funbo Åkerby, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>656182</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6639863</v>
+      </c>
+      <c r="S19" t="n">
+        <v>33</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-05-13</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-05-13</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>118237470</v>
+      </c>
+      <c r="B20" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Funbo Åkerby, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>656171</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6639830</v>
+      </c>
+      <c r="S20" t="n">
+        <v>31</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-05-13</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-05-13</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>118237475</v>
+      </c>
+      <c r="B21" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Funbo Åkerby, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>656153</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6639782</v>
+      </c>
+      <c r="S21" t="n">
+        <v>26</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-05-13</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-05-13</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>118237476</v>
+      </c>
+      <c r="B22" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Funbo Åkerby, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>656145</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6639736</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-05-13</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-05-13</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>118237480</v>
+      </c>
+      <c r="B23" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Funbo Åkerby, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>656132</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6639715</v>
+      </c>
+      <c r="S23" t="n">
+        <v>22</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-05-13</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-05-13</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>118237487</v>
+      </c>
+      <c r="B24" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Funbo Åkerby, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>656210</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6639877</v>
+      </c>
+      <c r="S24" t="n">
+        <v>15</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-05-13</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-05-13</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>109852562</v>
+      </c>
+      <c r="B25" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Funbo-Åkerby, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>655807</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6639709</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2023-05-05</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2023-05-05</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>118237472</v>
+      </c>
+      <c r="B26" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Funbo Åkerby, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>656158</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6639786</v>
+      </c>
+      <c r="S26" t="n">
+        <v>29</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-05-13</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-05-13</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>118237481</v>
+      </c>
+      <c r="B27" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Funbo Åkerby, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>656129</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6639711</v>
+      </c>
+      <c r="S27" t="n">
+        <v>21</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-05-13</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-05-13</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>118237483</v>
+      </c>
+      <c r="B28" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Funbo Åkerby, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>656097</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6639678</v>
+      </c>
+      <c r="S28" t="n">
+        <v>19</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Funbo</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-05-13</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-05-13</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
